--- a/projects_export.xlsx
+++ b/projects_export.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q164"/>
+  <dimension ref="A1:S167"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,22 +435,28 @@
         <v>serviceRequested</v>
       </c>
       <c r="L1" t="str">
+        <v>createdAt</v>
+      </c>
+      <c r="M1" t="str">
+        <v>projectTag</v>
+      </c>
+      <c r="N1" t="str">
+        <v>startDate</v>
+      </c>
+      <c r="O1" t="str">
+        <v>sendingInstitution</v>
+      </c>
+      <c r="P1" t="str">
+        <v>status</v>
+      </c>
+      <c r="Q1" t="str">
         <v>clientNames</v>
       </c>
-      <c r="M1" t="str">
-        <v>createdAt</v>
-      </c>
-      <c r="N1" t="str">
-        <v>projectTag</v>
-      </c>
-      <c r="O1" t="str">
-        <v>startDate</v>
-      </c>
-      <c r="P1" t="str">
-        <v>sendingInstitution</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>status</v>
+      <c r="R1" t="str">
+        <v>updatedAt</v>
+      </c>
+      <c r="S1" t="str">
+        <v>projectLead</v>
       </c>
     </row>
     <row r="2">
@@ -484,20 +490,23 @@
       <c r="J2" t="str">
         <v>PGC VISAYAS</v>
       </c>
-      <c r="M2" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N2" t="str">
+      <c r="L2" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M2" t="str">
         <v>PGCV</v>
       </c>
-      <c r="O2" s="1">
+      <c r="N2" s="1">
         <v>43525.000497685185</v>
       </c>
+      <c r="O2" t="str">
+        <v>N/A</v>
+      </c>
       <c r="P2" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="Q2" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R2" s="1">
+        <v>46071.45857638889</v>
       </c>
     </row>
     <row r="3">
@@ -531,20 +540,23 @@
       <c r="J3" t="str">
         <v>Rema C. Sibonga</v>
       </c>
-      <c r="M3" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N3" t="str">
+      <c r="L3" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M3" t="str">
         <v>GSStar</v>
       </c>
-      <c r="O3" s="1">
+      <c r="N3" s="1">
         <v>43903.000497685185</v>
       </c>
+      <c r="O3" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P3" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R3" s="1">
+        <v>46071.45857638889</v>
       </c>
     </row>
     <row r="4">
@@ -578,17 +590,20 @@
       <c r="J4" t="str">
         <v>Loina Henzel A. Delgado</v>
       </c>
-      <c r="M4" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N4" t="str">
+      <c r="L4" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M4" t="str">
         <v>TBI</v>
       </c>
+      <c r="O4" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P4" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R4" s="1">
+        <v>46071.45857638889</v>
       </c>
     </row>
     <row r="5">
@@ -622,17 +637,20 @@
       <c r="J5" t="str">
         <v>Mary Antonette F. Atilano</v>
       </c>
-      <c r="M5" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N5" t="str">
+      <c r="L5" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M5" t="str">
         <v>TGMPPEFET</v>
       </c>
+      <c r="O5" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P5" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R5" s="1">
+        <v>46071.45858796296</v>
       </c>
     </row>
     <row r="6">
@@ -666,20 +684,23 @@
       <c r="J6" t="str">
         <v>Nadelene Faith N. Cartago</v>
       </c>
-      <c r="M6" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N6" t="str">
+      <c r="L6" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M6" t="str">
         <v>Cartago</v>
       </c>
-      <c r="O6" s="1">
+      <c r="N6" s="1">
         <v>44015.000497685185</v>
       </c>
+      <c r="O6" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P6" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R6" s="1">
+        <v>46071.45858796296</v>
       </c>
     </row>
     <row r="7">
@@ -713,17 +734,20 @@
       <c r="J7" t="str">
         <v>Denise V. Miranda</v>
       </c>
-      <c r="M7" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N7" t="str">
+      <c r="L7" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M7" t="str">
         <v>Ice-Ice</v>
       </c>
+      <c r="O7" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P7" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q7" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R7" s="1">
+        <v>46071.45858796296</v>
       </c>
     </row>
     <row r="8">
@@ -757,17 +781,20 @@
       <c r="J8" t="str">
         <v>Wilson F. Medrocillo</v>
       </c>
-      <c r="M8" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N8" t="str">
+      <c r="L8" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M8" t="str">
         <v>Cuevas</v>
       </c>
+      <c r="O8" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P8" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R8" s="1">
+        <v>46071.45858796296</v>
       </c>
     </row>
     <row r="9">
@@ -801,20 +828,23 @@
       <c r="J9" t="str">
         <v>Leonilo F. Endoma</v>
       </c>
-      <c r="M9" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N9" t="str">
+      <c r="L9" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M9" t="str">
         <v>Endoma</v>
       </c>
-      <c r="O9" s="1">
+      <c r="N9" s="1">
         <v>44035.000497685185</v>
       </c>
+      <c r="O9" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P9" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q9" t="str">
         <v>Cancelled</v>
+      </c>
+      <c r="R9" s="1">
+        <v>46071.45858796296</v>
       </c>
     </row>
     <row r="10">
@@ -848,17 +878,20 @@
       <c r="J10" t="str">
         <v xml:space="preserve">Ma. Novem Grace Ylayron </v>
       </c>
-      <c r="M10" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N10" t="str">
+      <c r="L10" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M10" t="str">
         <v>Panay Marfish Project</v>
       </c>
+      <c r="O10" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P10" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R10" s="1">
+        <v>46071.458599537036</v>
       </c>
     </row>
     <row r="11">
@@ -892,20 +925,23 @@
       <c r="J11" t="str">
         <v>Pretty Lee Silva</v>
       </c>
-      <c r="M11" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N11" t="str">
+      <c r="L11" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M11" t="str">
         <v>Silva</v>
       </c>
-      <c r="O11" s="1">
+      <c r="N11" s="1">
         <v>44062.000497685185</v>
       </c>
+      <c r="O11" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P11" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q11" t="str">
         <v>Cancelled</v>
+      </c>
+      <c r="R11" s="1">
+        <v>46071.458599537036</v>
       </c>
     </row>
     <row r="12">
@@ -939,20 +975,23 @@
       <c r="J12" t="str">
         <v>Leni G. Yap-Dejeto</v>
       </c>
-      <c r="M12" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N12" t="str">
+      <c r="L12" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M12" t="str">
         <v>Glycogen</v>
       </c>
-      <c r="O12" s="1">
+      <c r="N12" s="1">
         <v>44250.000497685185</v>
       </c>
+      <c r="O12" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P12" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q12" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R12" s="1">
+        <v>46071.458599537036</v>
       </c>
     </row>
     <row r="13">
@@ -986,17 +1025,20 @@
       <c r="J13" t="str">
         <v>Roxanne Cabebe</v>
       </c>
-      <c r="M13" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N13" t="str">
+      <c r="L13" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M13" t="str">
         <v>DNA Barcoding</v>
       </c>
+      <c r="O13" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P13" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q13" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R13" s="1">
+        <v>46071.458599537036</v>
       </c>
     </row>
     <row r="14">
@@ -1030,20 +1072,23 @@
       <c r="J14" t="str">
         <v>Albert C. Noblezada</v>
       </c>
-      <c r="M14" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N14" t="str">
+      <c r="L14" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M14" t="str">
         <v>Noblezada</v>
       </c>
-      <c r="O14" s="1">
+      <c r="N14" s="1">
         <v>44302.000497685185</v>
       </c>
+      <c r="O14" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P14" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q14" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R14" s="1">
+        <v>46071.45861111111</v>
       </c>
     </row>
     <row r="15">
@@ -1077,17 +1122,20 @@
       <c r="J15" t="str">
         <v>Jasper D. Pacho</v>
       </c>
-      <c r="M15" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N15" t="str">
+      <c r="L15" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M15" t="str">
         <v>GeM-PHIL</v>
       </c>
+      <c r="O15" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P15" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q15" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R15" s="1">
+        <v>46071.45861111111</v>
       </c>
     </row>
     <row r="16">
@@ -1121,17 +1169,20 @@
       <c r="J16" t="str">
         <v>Kristina Samantha Lacson</v>
       </c>
-      <c r="M16" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N16" t="str">
+      <c r="L16" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M16" t="str">
         <v>Calamansi Project</v>
       </c>
+      <c r="O16" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P16" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q16" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R16" s="1">
+        <v>46071.45861111111</v>
       </c>
     </row>
     <row r="17">
@@ -1165,20 +1216,23 @@
       <c r="J17" t="str">
         <v>Carolyn T. Mejares</v>
       </c>
-      <c r="M17" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N17" t="str">
+      <c r="L17" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M17" t="str">
         <v>Mejares</v>
       </c>
-      <c r="O17" s="1">
+      <c r="N17" s="1">
         <v>44435.000497685185</v>
       </c>
+      <c r="O17" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P17" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q17" t="str">
         <v>Cancelled</v>
+      </c>
+      <c r="R17" s="1">
+        <v>46071.45861111111</v>
       </c>
     </row>
     <row r="18">
@@ -1212,20 +1266,23 @@
       <c r="J18" t="str">
         <v>Rowena E. Cadiz</v>
       </c>
-      <c r="M18" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N18" t="str">
+      <c r="L18" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M18" t="str">
         <v>AquaFeed</v>
       </c>
-      <c r="O18" s="1">
+      <c r="N18" s="1">
         <v>44579.000497685185</v>
       </c>
+      <c r="O18" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P18" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q18" t="str">
         <v>Cancelled</v>
+      </c>
+      <c r="R18" s="1">
+        <v>46071.45862268518</v>
       </c>
     </row>
     <row r="19">
@@ -1259,17 +1316,20 @@
       <c r="J19" t="str">
         <v>Shea Kathleen P. Guinto</v>
       </c>
-      <c r="M19" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N19" t="str">
+      <c r="L19" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M19" t="str">
         <v>PFZ</v>
       </c>
+      <c r="O19" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P19" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q19" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R19" s="1">
+        <v>46071.45863425926</v>
       </c>
     </row>
     <row r="20">
@@ -1303,20 +1363,23 @@
       <c r="J20" t="str">
         <v>Rother M. Gaudiel</v>
       </c>
-      <c r="M20" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N20" t="str">
+      <c r="L20" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M20" t="str">
         <v>RGaudiel</v>
       </c>
-      <c r="O20" s="1">
+      <c r="N20" s="1">
         <v>44622.000497685185</v>
       </c>
+      <c r="O20" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P20" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q20" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R20" s="1">
+        <v>46071.45863425926</v>
       </c>
     </row>
     <row r="21">
@@ -1350,20 +1413,23 @@
       <c r="J21" t="str">
         <v>John Rey F. Rasgo</v>
       </c>
-      <c r="M21" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N21" t="str">
+      <c r="L21" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M21" t="str">
         <v>JRRasgo</v>
       </c>
-      <c r="O21" s="1">
+      <c r="N21" s="1">
         <v>44624.000497685185</v>
       </c>
+      <c r="O21" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P21" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q21" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R21" s="1">
+        <v>46071.45863425926</v>
       </c>
     </row>
     <row r="22">
@@ -1397,20 +1463,23 @@
       <c r="J22" t="str">
         <v>Luke Dranoel D. Atencio</v>
       </c>
-      <c r="M22" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N22" t="str">
+      <c r="L22" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M22" t="str">
         <v>LDAtencio</v>
       </c>
-      <c r="O22" s="1">
+      <c r="N22" s="1">
         <v>44628.000497685185</v>
       </c>
+      <c r="O22" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P22" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q22" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R22" s="1">
+        <v>46071.45863425926</v>
       </c>
     </row>
     <row r="23">
@@ -1444,20 +1513,23 @@
       <c r="J23" t="str">
         <v>Whelver N. Surnido</v>
       </c>
-      <c r="M23" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N23" t="str">
+      <c r="L23" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M23" t="str">
         <v>WNSurnido</v>
       </c>
-      <c r="O23" s="1">
+      <c r="N23" s="1">
         <v>44634.000497685185</v>
       </c>
+      <c r="O23" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P23" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q23" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R23" s="1">
+        <v>46071.458645833336</v>
       </c>
     </row>
     <row r="24">
@@ -1491,20 +1563,23 @@
       <c r="J24" t="str">
         <v>Kingsley John de los Santos</v>
       </c>
-      <c r="M24" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N24" t="str">
+      <c r="L24" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M24" t="str">
         <v>KDSantos</v>
       </c>
-      <c r="O24" s="1">
+      <c r="N24" s="1">
         <v>44644.000497685185</v>
       </c>
+      <c r="O24" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P24" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q24" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R24" s="1">
+        <v>46071.458645833336</v>
       </c>
     </row>
     <row r="25">
@@ -1538,20 +1613,23 @@
       <c r="J25" t="str">
         <v>Karl C. Abismo</v>
       </c>
-      <c r="M25" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N25" t="str">
+      <c r="L25" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M25" t="str">
         <v>KCAbismo</v>
       </c>
-      <c r="O25" s="1">
+      <c r="N25" s="1">
         <v>44645.000497685185</v>
       </c>
+      <c r="O25" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P25" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q25" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R25" s="1">
+        <v>46071.458645833336</v>
       </c>
     </row>
     <row r="26">
@@ -1585,20 +1663,23 @@
       <c r="J26" t="str">
         <v>Benedict Maralit</v>
       </c>
-      <c r="M26" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N26" t="str">
+      <c r="L26" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M26" t="str">
         <v>Retrospective Biosurveillance</v>
       </c>
-      <c r="O26" s="1">
+      <c r="N26" s="1">
         <v>44680.000497685185</v>
       </c>
+      <c r="O26" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P26" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q26" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R26" s="1">
+        <v>46071.458645833336</v>
       </c>
     </row>
     <row r="27">
@@ -1632,20 +1713,23 @@
       <c r="J27" t="str">
         <v>Philip Alviola</v>
       </c>
-      <c r="M27" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N27" t="str">
+      <c r="L27" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M27" t="str">
         <v>Bats</v>
       </c>
-      <c r="O27" s="1">
+      <c r="N27" s="1">
         <v>44680.000497685185</v>
       </c>
+      <c r="O27" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P27" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q27" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R27" s="1">
+        <v>46071.458645833336</v>
       </c>
     </row>
     <row r="28">
@@ -1679,20 +1763,23 @@
       <c r="J28" t="str">
         <v>Persie Persie Mark Sienes</v>
       </c>
-      <c r="M28" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N28" t="str">
+      <c r="L28" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M28" t="str">
         <v>PGCV_Deer WGS</v>
       </c>
-      <c r="O28" s="1">
+      <c r="N28" s="1">
         <v>44682.000497685185</v>
       </c>
+      <c r="O28" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P28" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q28" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R28" s="1">
+        <v>46071.458645833336</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -1727,20 +1814,23 @@
       <c r="J29" t="str">
         <v>Beverly T. Jaspe</v>
       </c>
-      <c r="M29" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N29" t="str">
+      <c r="L29" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M29" t="str">
         <v>Pholas</v>
       </c>
-      <c r="O29" s="1">
+      <c r="N29" s="1">
         <v>44682.000497685185</v>
       </c>
+      <c r="O29" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P29" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q29" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R29" s="1">
+        <v>46071.458657407406</v>
       </c>
     </row>
     <row r="30">
@@ -1774,20 +1864,23 @@
       <c r="J30" t="str">
         <v>Camille Rose T. Mueda</v>
       </c>
-      <c r="M30" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N30" t="str">
+      <c r="L30" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M30" t="str">
         <v>Mueda</v>
       </c>
-      <c r="O30" s="1">
+      <c r="N30" s="1">
         <v>44718.000497685185</v>
       </c>
+      <c r="O30" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P30" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q30" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R30" s="1">
+        <v>46071.458657407406</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
@@ -1822,17 +1915,20 @@
       <c r="J31" t="str">
         <v>Kneessa Louie G. Dato-on</v>
       </c>
-      <c r="M31" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N31" t="str">
+      <c r="L31" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M31" t="str">
         <v>Thrausto</v>
       </c>
+      <c r="O31" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P31" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q31" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R31" s="1">
+        <v>46071.458657407406</v>
       </c>
     </row>
     <row r="32">
@@ -1866,20 +1962,23 @@
       <c r="J32" t="str">
         <v>Zeth Rodario Bebit</v>
       </c>
-      <c r="M32" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N32" t="str">
+      <c r="L32" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M32" t="str">
         <v>Bebit</v>
       </c>
-      <c r="O32" s="1">
+      <c r="N32" s="1">
         <v>44729.000497685185</v>
       </c>
+      <c r="O32" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P32" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q32" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R32" s="1">
+        <v>46071.458657407406</v>
       </c>
     </row>
     <row r="33">
@@ -1913,19 +2012,19 @@
       <c r="J33" t="str">
         <v>Angel Queenee D. Dequito</v>
       </c>
-      <c r="M33" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N33" t="str">
+      <c r="L33" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M33" t="str">
         <v>TGMPPEFET</v>
       </c>
-      <c r="O33" s="1">
+      <c r="N33" s="1">
         <v>44754.000497685185</v>
       </c>
+      <c r="O33" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P33" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q33" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -1960,17 +2059,20 @@
       <c r="J34" t="str">
         <v>Isabel Grace Gatpatan</v>
       </c>
-      <c r="M34" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N34" t="str">
+      <c r="L34" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M34" t="str">
         <v>Cabulong, (OM,CM)</v>
       </c>
+      <c r="O34" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P34" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q34" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R34" s="1">
+        <v>46071.45866898148</v>
       </c>
     </row>
     <row r="35">
@@ -2004,17 +2106,20 @@
       <c r="J35" t="str">
         <v>Frenche B. Hechanova</v>
       </c>
-      <c r="M35" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N35" t="str">
+      <c r="L35" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M35" t="str">
         <v>DeNoVac</v>
       </c>
+      <c r="O35" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P35" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q35" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R35" s="1">
+        <v>46071.45866898148</v>
       </c>
     </row>
     <row r="36">
@@ -2048,17 +2153,20 @@
       <c r="J36" t="str">
         <v>Arnel Adrian Rara</v>
       </c>
-      <c r="M36" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N36" t="str">
+      <c r="L36" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M36" t="str">
         <v>Microalgae</v>
       </c>
+      <c r="O36" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P36" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q36" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R36" s="1">
+        <v>46071.45866898148</v>
       </c>
     </row>
     <row r="37">
@@ -2092,20 +2200,23 @@
       <c r="J37" t="str">
         <v>Pauline Anne Lamela</v>
       </c>
-      <c r="M37" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N37" t="str">
+      <c r="L37" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M37" t="str">
         <v>Lamela</v>
       </c>
-      <c r="O37" s="1">
+      <c r="N37" s="1">
         <v>44902.000497685185</v>
       </c>
+      <c r="O37" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P37" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q37" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R37" s="1">
+        <v>46071.45866898148</v>
       </c>
     </row>
     <row r="38">
@@ -2139,17 +2250,20 @@
       <c r="J38" t="str">
         <v>Edcel T. Resano</v>
       </c>
-      <c r="M38" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N38" t="str">
+      <c r="L38" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M38" t="str">
         <v>Cabarles et al</v>
       </c>
+      <c r="O38" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P38" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q38" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R38" s="1">
+        <v>46071.45866898148</v>
       </c>
     </row>
     <row r="39">
@@ -2183,20 +2297,23 @@
       <c r="J39" t="str">
         <v>Dr. Sitti Zayda Halun</v>
       </c>
-      <c r="M39" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N39" t="str">
+      <c r="L39" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M39" t="str">
         <v>Halun</v>
       </c>
-      <c r="O39" s="1">
+      <c r="N39" s="1">
         <v>44964.000497685185</v>
       </c>
+      <c r="O39" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P39" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q39" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R39" s="1">
+        <v>46071.45868055556</v>
       </c>
     </row>
     <row r="40">
@@ -2230,19 +2347,19 @@
       <c r="J40" t="str">
         <v>PGC Visayas</v>
       </c>
-      <c r="M40" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N40" t="str">
+      <c r="L40" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M40" t="str">
         <v>Dugong - Miagao</v>
       </c>
-      <c r="O40" s="1">
+      <c r="N40" s="1">
         <v>44993.000497685185</v>
       </c>
+      <c r="O40" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P40" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q40" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -2277,20 +2394,23 @@
       <c r="J41" t="str">
         <v>Elsie Y. Guibone</v>
       </c>
-      <c r="M41" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N41" t="str">
+      <c r="L41" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M41" t="str">
         <v>Lernaea</v>
       </c>
-      <c r="O41" s="1">
+      <c r="N41" s="1">
         <v>44999.000497685185</v>
       </c>
+      <c r="O41" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P41" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q41" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R41" s="1">
+        <v>46071.45868055556</v>
       </c>
     </row>
     <row r="42">
@@ -2324,20 +2444,23 @@
       <c r="J42" t="str">
         <v>Claire Samantha Juanico</v>
       </c>
-      <c r="M42" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N42" t="str">
+      <c r="L42" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M42" t="str">
         <v>Fish Gut</v>
       </c>
-      <c r="O42" s="1">
+      <c r="N42" s="1">
         <v>44999.000497685185</v>
       </c>
+      <c r="O42" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P42" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q42" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R42" s="1">
+        <v>46071.45868055556</v>
       </c>
     </row>
     <row r="43" xml:space="preserve">
@@ -2372,17 +2495,20 @@
       <c r="J43" t="str">
         <v>Karmelie Jane Monaya</v>
       </c>
-      <c r="M43" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N43" t="str">
+      <c r="L43" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M43" t="str">
         <v>Lumapan</v>
       </c>
+      <c r="O43" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P43" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q43" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R43" s="1">
+        <v>46071.45868055556</v>
       </c>
     </row>
     <row r="44">
@@ -2416,20 +2542,23 @@
       <c r="J44" t="str">
         <v>Beatrice L. Anacita</v>
       </c>
-      <c r="M44" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N44" t="str">
+      <c r="L44" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M44" t="str">
         <v>Anacita</v>
       </c>
-      <c r="O44" s="1">
+      <c r="N44" s="1">
         <v>45035.000497685185</v>
       </c>
+      <c r="O44" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P44" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q44" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R44" s="1">
+        <v>46071.45869212963</v>
       </c>
     </row>
     <row r="45">
@@ -2463,20 +2592,23 @@
       <c r="J45" t="str">
         <v>Kyla Julienne P. Talaman</v>
       </c>
-      <c r="M45" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N45" t="str">
+      <c r="L45" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M45" t="str">
         <v>Talaman</v>
       </c>
-      <c r="O45" s="1">
+      <c r="N45" s="1">
         <v>45035.000497685185</v>
       </c>
+      <c r="O45" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P45" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q45" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R45" s="1">
+        <v>46071.45869212963</v>
       </c>
     </row>
     <row r="46">
@@ -2510,20 +2642,23 @@
       <c r="J46" t="str">
         <v>Trisha Marie Santos</v>
       </c>
-      <c r="M46" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N46" t="str">
+      <c r="L46" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M46" t="str">
         <v>Santos</v>
       </c>
-      <c r="O46" s="1">
+      <c r="N46" s="1">
         <v>45036.000497685185</v>
       </c>
+      <c r="O46" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P46" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q46" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R46" s="1">
+        <v>46071.45869212963</v>
       </c>
     </row>
     <row r="47">
@@ -2557,20 +2692,23 @@
       <c r="J47" t="str">
         <v>Trisha Catalya</v>
       </c>
-      <c r="M47" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N47" t="str">
+      <c r="L47" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M47" t="str">
         <v>Catalya</v>
       </c>
-      <c r="O47" s="1">
+      <c r="N47" s="1">
         <v>45051.000497685185</v>
       </c>
+      <c r="O47" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P47" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q47" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R47" s="1">
+        <v>46071.45869212963</v>
       </c>
     </row>
     <row r="48">
@@ -2604,20 +2742,23 @@
       <c r="J48" t="str">
         <v>Josie Mar G. Cabalo</v>
       </c>
-      <c r="M48" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N48" t="str">
+      <c r="L48" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M48" t="str">
         <v>Cabalo</v>
       </c>
-      <c r="O48" s="1">
+      <c r="N48" s="1">
         <v>45051.000497685185</v>
       </c>
+      <c r="O48" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P48" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q48" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R48" s="1">
+        <v>46071.458703703705</v>
       </c>
     </row>
     <row r="49" xml:space="preserve">
@@ -2652,20 +2793,23 @@
       <c r="J49" t="str">
         <v>Elize Margareth C. Sibulan</v>
       </c>
-      <c r="M49" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N49" t="str">
+      <c r="L49" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M49" t="str">
         <v>LN - Gregorio, Sibulan</v>
       </c>
-      <c r="O49" s="1">
+      <c r="N49" s="1">
         <v>45062.000497685185</v>
       </c>
+      <c r="O49" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P49" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q49" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R49" s="1">
+        <v>46071.458703703705</v>
       </c>
     </row>
     <row r="50">
@@ -2699,20 +2843,23 @@
       <c r="J50" t="str">
         <v>Ella Marie Kristine Baldove</v>
       </c>
-      <c r="M50" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N50" t="str">
+      <c r="L50" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M50" t="str">
         <v>Feedmix</v>
       </c>
-      <c r="O50" s="1">
+      <c r="N50" s="1">
         <v>45082.000497685185</v>
       </c>
+      <c r="O50" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P50" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q50" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R50" s="1">
+        <v>46071.458715277775</v>
       </c>
     </row>
     <row r="51">
@@ -2746,20 +2893,23 @@
       <c r="J51" t="str">
         <v>Abigail F. Padua</v>
       </c>
-      <c r="M51" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N51" t="str">
+      <c r="L51" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M51" t="str">
         <v>LN - Padua</v>
       </c>
-      <c r="O51" s="1">
+      <c r="N51" s="1">
         <v>45083.000497685185</v>
       </c>
+      <c r="O51" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P51" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q51" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R51" s="1">
+        <v>46071.458715277775</v>
       </c>
     </row>
     <row r="52">
@@ -2773,7 +2923,7 @@
         <v/>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="E52" t="str">
         <v>In-House</v>
@@ -2793,17 +2943,23 @@
       <c r="J52" t="str">
         <v>Jojie P. Gereza</v>
       </c>
-      <c r="M52" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N52" t="str">
+      <c r="L52" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M52" t="str">
         <v>DENR</v>
       </c>
+      <c r="N52" s="1">
+        <v>45272.75403935185</v>
+      </c>
+      <c r="O52" t="str">
+        <v>Government</v>
+      </c>
       <c r="P52" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q52" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R52" s="1">
+        <v>46071.458715277775</v>
       </c>
     </row>
     <row r="53">
@@ -2837,20 +2993,23 @@
       <c r="J53" t="str">
         <v>Ma Jowina Galarion</v>
       </c>
-      <c r="M53" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N53" t="str">
+      <c r="L53" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M53" t="str">
         <v>Dengue Seq</v>
       </c>
-      <c r="O53" s="1">
+      <c r="N53" s="1">
         <v>45091.000497685185</v>
       </c>
+      <c r="O53" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P53" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q53" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R53" s="1">
+        <v>46071.458715277775</v>
       </c>
     </row>
     <row r="54">
@@ -2884,17 +3043,20 @@
       <c r="J54" t="str">
         <v>Jan Felnesh Exe Bagacay</v>
       </c>
-      <c r="M54" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N54" t="str">
+      <c r="L54" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M54" t="str">
         <v>AQFP</v>
       </c>
+      <c r="O54" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P54" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q54" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R54" s="1">
+        <v>46071.458715277775</v>
       </c>
     </row>
     <row r="55">
@@ -2928,20 +3090,23 @@
       <c r="J55" t="str">
         <v>Sheryll Mesa</v>
       </c>
-      <c r="M55" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N55" t="str">
+      <c r="L55" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M55" t="str">
         <v>BFAR Sperm Whale</v>
       </c>
-      <c r="O55" s="1">
+      <c r="N55" s="1">
         <v>45125.000497685185</v>
       </c>
+      <c r="O55" t="str">
+        <v>International</v>
+      </c>
       <c r="P55" t="str">
-        <v>International</v>
-      </c>
-      <c r="Q55" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R55" s="1">
+        <v>46071.45872685185</v>
       </c>
     </row>
     <row r="56">
@@ -2975,20 +3140,23 @@
       <c r="J56" t="str">
         <v>Krshna Mahakaola A. Dueñas</v>
       </c>
-      <c r="M56" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N56" t="str">
+      <c r="L56" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M56" t="str">
         <v>LN - Dueñas</v>
       </c>
-      <c r="O56" s="1">
+      <c r="N56" s="1">
         <v>45140.000497685185</v>
       </c>
+      <c r="O56" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P56" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q56" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R56" s="1">
+        <v>46071.45872685185</v>
       </c>
     </row>
     <row r="57">
@@ -3022,17 +3190,20 @@
       <c r="J57" t="str">
         <v>Stephen G. Sabinay</v>
       </c>
-      <c r="M57" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N57" t="str">
+      <c r="L57" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M57" t="str">
         <v>V. cholerae (WVSU)</v>
       </c>
+      <c r="O57" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P57" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q57" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R57" s="1">
+        <v>46071.45872685185</v>
       </c>
     </row>
     <row r="58">
@@ -3066,20 +3237,23 @@
       <c r="J58" t="str">
         <v>Joseph Faisan Jr.</v>
       </c>
-      <c r="M58" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N58" t="str">
+      <c r="L58" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M58" t="str">
         <v>SEAFDEC (Eel)</v>
       </c>
-      <c r="O58" s="1">
+      <c r="N58" s="1">
         <v>45167.000497685185</v>
       </c>
+      <c r="O58" t="str">
+        <v>International</v>
+      </c>
       <c r="P58" t="str">
-        <v>International</v>
-      </c>
-      <c r="Q58" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R58" s="1">
+        <v>46071.45872685185</v>
       </c>
     </row>
     <row r="59">
@@ -3113,20 +3287,23 @@
       <c r="J59" t="str">
         <v>Nadine Belas</v>
       </c>
-      <c r="M59" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N59" t="str">
+      <c r="L59" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M59" t="str">
         <v>Kapis</v>
       </c>
-      <c r="O59" s="1">
+      <c r="N59" s="1">
         <v>45180.000497685185</v>
       </c>
+      <c r="O59" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P59" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q59" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R59" s="1">
+        <v>46071.45873842593</v>
       </c>
     </row>
     <row r="60">
@@ -3160,17 +3337,20 @@
       <c r="J60" t="str">
         <v>Eric Zeus C. Rizo</v>
       </c>
-      <c r="M60" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N60" t="str">
+      <c r="L60" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M60" t="str">
         <v>DAFZooMacro</v>
       </c>
+      <c r="O60" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P60" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q60" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R60" s="1">
+        <v>46071.45873842593</v>
       </c>
     </row>
     <row r="61">
@@ -3204,19 +3384,19 @@
       <c r="J61" t="str">
         <v>PGC VISAYAS</v>
       </c>
-      <c r="M61" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N61" t="str">
+      <c r="L61" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M61" t="str">
         <v>Commercial Alcohol Preservation</v>
       </c>
-      <c r="O61" s="1">
+      <c r="N61" s="1">
         <v>45222.000497685185</v>
       </c>
+      <c r="O61" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P61" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q61" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -3251,20 +3431,23 @@
       <c r="J62" t="str">
         <v>Viva Princess A. Basa</v>
       </c>
-      <c r="M62" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N62" t="str">
+      <c r="L62" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M62" t="str">
         <v>MinSU Bioinfo</v>
       </c>
-      <c r="O62" s="1">
+      <c r="N62" s="1">
         <v>45239.000497685185</v>
       </c>
+      <c r="O62" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P62" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q62" t="str">
         <v>Cancelled</v>
+      </c>
+      <c r="R62" s="1">
+        <v>46071.45875</v>
       </c>
     </row>
     <row r="63">
@@ -3298,17 +3481,20 @@
       <c r="J63" t="str">
         <v>Christine Teves</v>
       </c>
-      <c r="M63" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N63" t="str">
+      <c r="L63" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M63" t="str">
         <v>PIPP - EIDR</v>
       </c>
+      <c r="O63" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P63" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q63" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R63" s="1">
+        <v>46071.45875</v>
       </c>
     </row>
     <row r="64">
@@ -3342,20 +3528,23 @@
       <c r="J64" t="str">
         <v>LC May C. Gasit</v>
       </c>
-      <c r="M64" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N64" t="str">
+      <c r="L64" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M64" t="str">
         <v>Blood Cockle Project</v>
       </c>
-      <c r="O64" s="1">
+      <c r="N64" s="1">
         <v>45247.000497685185</v>
       </c>
+      <c r="O64" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P64" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q64" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R64" s="1">
+        <v>46071.45875</v>
       </c>
     </row>
     <row r="65">
@@ -3389,19 +3578,19 @@
       <c r="J65" t="str">
         <v>Jojie P. Gereza</v>
       </c>
-      <c r="M65" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N65" t="str">
+      <c r="L65" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M65" t="str">
         <v>DENR - Snake</v>
       </c>
-      <c r="O65" s="1">
+      <c r="N65" s="1">
         <v>45272.000497685185</v>
       </c>
+      <c r="O65" t="str">
+        <v>Government</v>
+      </c>
       <c r="P65" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q65" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -3436,20 +3625,23 @@
       <c r="J66" t="str">
         <v>Jonie C. Yee, Ph.D.</v>
       </c>
-      <c r="M66" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N66" t="str">
+      <c r="L66" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M66" t="str">
         <v>Nat Prod (USC) - Dr. Yee</v>
       </c>
-      <c r="O66" s="1">
+      <c r="N66" s="1">
         <v>45316.000497685185</v>
       </c>
+      <c r="O66" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P66" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q66" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R66" s="1">
+        <v>46071.458761574075</v>
       </c>
     </row>
     <row r="67">
@@ -3483,19 +3675,19 @@
       <c r="J67" t="str">
         <v>PGC Visayas</v>
       </c>
-      <c r="M67" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N67" t="str">
+      <c r="L67" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M67" t="str">
         <v>Diwal WGS</v>
       </c>
-      <c r="O67" s="1">
+      <c r="N67" s="1">
         <v>45321.000497685185</v>
       </c>
+      <c r="O67" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P67" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q67" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -3530,19 +3722,19 @@
       <c r="J68" t="str">
         <v>PGC Visayas</v>
       </c>
-      <c r="M68" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N68" t="str">
+      <c r="L68" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M68" t="str">
         <v>Ambergris</v>
       </c>
-      <c r="O68" s="1">
+      <c r="N68" s="1">
         <v>45321.000497685185</v>
       </c>
+      <c r="O68" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P68" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q68" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -3577,20 +3769,23 @@
       <c r="J69" t="str">
         <v>Kaylen Yvon K. Jalandoni</v>
       </c>
-      <c r="M69" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N69" t="str">
+      <c r="L69" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M69" t="str">
         <v>Jalandoni - Type II</v>
       </c>
-      <c r="O69" s="1">
+      <c r="N69" s="1">
         <v>45329.000497685185</v>
       </c>
+      <c r="O69" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P69" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q69" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R69" s="1">
+        <v>46071.458761574075</v>
       </c>
     </row>
     <row r="70">
@@ -3624,20 +3819,23 @@
       <c r="J70" t="str">
         <v>Ram Nikko U. Delegero</v>
       </c>
-      <c r="M70" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N70" t="str">
+      <c r="L70" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M70" t="str">
         <v>Delegero - Type II</v>
       </c>
-      <c r="O70" s="1">
+      <c r="N70" s="1">
         <v>45335.000497685185</v>
       </c>
+      <c r="O70" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P70" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q70" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R70" s="1">
+        <v>46071.45877314815</v>
       </c>
     </row>
     <row r="71">
@@ -3671,17 +3869,20 @@
       <c r="J71" t="str">
         <v>Jordan F. Dorado</v>
       </c>
-      <c r="M71" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N71" t="str">
+      <c r="L71" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M71" t="str">
         <v>Gastropod (RSU)</v>
       </c>
+      <c r="O71" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P71" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q71" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R71" s="1">
+        <v>46071.45877314815</v>
       </c>
     </row>
     <row r="72">
@@ -3715,17 +3916,20 @@
       <c r="J72" t="str">
         <v>Caryl Anne G. Abulencia</v>
       </c>
-      <c r="M72" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N72" t="str">
+      <c r="L72" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M72" t="str">
         <v>Capiz Shell (WVSU)</v>
       </c>
+      <c r="O72" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P72" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q72" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R72" s="1">
+        <v>46071.4587962963</v>
       </c>
     </row>
     <row r="73">
@@ -3759,20 +3963,23 @@
       <c r="J73" t="str">
         <v>Dianne A. Peralta</v>
       </c>
-      <c r="M73" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N73" t="str">
+      <c r="L73" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M73" t="str">
         <v>DMMMSU - Amplicon</v>
       </c>
-      <c r="O73" s="1">
+      <c r="N73" s="1">
         <v>45355.000497685185</v>
       </c>
+      <c r="O73" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P73" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q73" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R73" s="1">
+        <v>46071.458819444444</v>
       </c>
     </row>
     <row r="74">
@@ -3806,19 +4013,19 @@
       <c r="J74" t="str">
         <v>Dianne A. Peralta</v>
       </c>
-      <c r="M74" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N74" t="str">
+      <c r="L74" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M74" t="str">
         <v>DMMMSU - 16s</v>
       </c>
-      <c r="O74" s="1">
+      <c r="N74" s="1">
         <v>45355.000497685185</v>
       </c>
+      <c r="O74" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P74" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q74" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -3853,19 +4060,19 @@
       <c r="J75" t="str">
         <v>Dianne A. Peralta</v>
       </c>
-      <c r="M75" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N75" t="str">
+      <c r="L75" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M75" t="str">
         <v>Sea Cucumber (16s)</v>
       </c>
-      <c r="O75" s="1">
+      <c r="N75" s="1">
         <v>45355.000497685185</v>
       </c>
+      <c r="O75" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P75" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q75" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -3900,20 +4107,23 @@
       <c r="J76" t="str">
         <v>Mae Dell S. Silfavan</v>
       </c>
-      <c r="M76" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N76" t="str">
+      <c r="L76" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M76" t="str">
         <v>Seaweed (BSF) A</v>
       </c>
-      <c r="O76" s="1">
+      <c r="N76" s="1">
         <v>45364.000497685185</v>
       </c>
+      <c r="O76" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P76" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q76" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R76" s="1">
+        <v>46071.458819444444</v>
       </c>
     </row>
     <row r="77">
@@ -3947,20 +4157,23 @@
       <c r="J77" t="str">
         <v>Jinelyn D. Kapaw-an</v>
       </c>
-      <c r="M77" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N77" t="str">
+      <c r="L77" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M77" t="str">
         <v>Seaweed (BSF) B</v>
       </c>
-      <c r="O77" s="1">
+      <c r="N77" s="1">
         <v>45364.000497685185</v>
       </c>
+      <c r="O77" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P77" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q77" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R77" s="1">
+        <v>46071.458819444444</v>
       </c>
     </row>
     <row r="78">
@@ -3994,20 +4207,23 @@
       <c r="J78" t="str">
         <v>Princess Sarah Gabiota</v>
       </c>
-      <c r="M78" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N78" t="str">
+      <c r="L78" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M78" t="str">
         <v>Seaweed (BSF) C</v>
       </c>
-      <c r="O78" s="1">
+      <c r="N78" s="1">
         <v>45364.000497685185</v>
       </c>
+      <c r="O78" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P78" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q78" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R78" s="1">
+        <v>46071.45883101852</v>
       </c>
     </row>
     <row r="79">
@@ -4041,17 +4257,20 @@
       <c r="J79" t="str">
         <v>Kharl Marx Adorado</v>
       </c>
-      <c r="M79" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N79" t="str">
+      <c r="L79" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M79" t="str">
         <v>Corals</v>
       </c>
+      <c r="O79" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P79" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q79" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R79" s="1">
+        <v>46071.45883101852</v>
       </c>
     </row>
     <row r="80">
@@ -4085,19 +4304,19 @@
       <c r="J80" t="str">
         <v>-</v>
       </c>
-      <c r="M80" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N80" t="str">
+      <c r="L80" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M80" t="str">
         <v>Tetraselmis</v>
       </c>
-      <c r="O80" s="1">
+      <c r="N80" s="1">
         <v>45364.000497685185</v>
       </c>
+      <c r="O80" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P80" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q80" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -4132,20 +4351,23 @@
       <c r="J81" t="str">
         <v>Kristina Casandra Pava</v>
       </c>
-      <c r="M81" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N81" t="str">
+      <c r="L81" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M81" t="str">
         <v>Pava - Bioinfo</v>
       </c>
-      <c r="O81" s="1">
+      <c r="N81" s="1">
         <v>45364.000497685185</v>
       </c>
+      <c r="O81" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P81" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q81" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R81" s="1">
+        <v>46071.45884259259</v>
       </c>
     </row>
     <row r="82">
@@ -4179,20 +4401,23 @@
       <c r="J82" t="str">
         <v>Marielle B. Chu</v>
       </c>
-      <c r="M82" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N82" t="str">
+      <c r="L82" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M82" t="str">
         <v>UPHSI - Chu</v>
       </c>
-      <c r="O82" s="1">
+      <c r="N82" s="1">
         <v>45362.000497685185</v>
       </c>
+      <c r="O82" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P82" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q82" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R82" s="1">
+        <v>46071.45884259259</v>
       </c>
     </row>
     <row r="83">
@@ -4226,19 +4451,19 @@
       <c r="J83" t="str">
         <v>Clarissa L. Gomez</v>
       </c>
-      <c r="M83" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N83" t="str">
+      <c r="L83" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M83" t="str">
         <v>Vibrio - Bioinfo</v>
       </c>
-      <c r="O83" s="1">
+      <c r="N83" s="1">
         <v>45378.000497685185</v>
       </c>
+      <c r="O83" t="str">
+        <v>Government</v>
+      </c>
       <c r="P83" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q83" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -4273,17 +4498,20 @@
       <c r="J84" t="str">
         <v>Joshua Miguel Javelosa</v>
       </c>
-      <c r="M84" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N84" t="str">
+      <c r="L84" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M84" t="str">
         <v>USLS - gene expression</v>
       </c>
+      <c r="O84" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P84" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q84" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R84" s="1">
+        <v>46071.45885416667</v>
       </c>
     </row>
     <row r="85">
@@ -4317,17 +4545,20 @@
       <c r="J85" t="str">
         <v>Elizabeth D. Fernandez</v>
       </c>
-      <c r="M85" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N85" t="str">
+      <c r="L85" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M85" t="str">
         <v>USLS - algae</v>
       </c>
+      <c r="O85" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P85" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q85" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R85" s="1">
+        <v>46071.45885416667</v>
       </c>
     </row>
     <row r="86">
@@ -4361,17 +4592,20 @@
       <c r="J86" t="str">
         <v>Carmelo del Castillo</v>
       </c>
-      <c r="M86" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N86" t="str">
+      <c r="L86" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M86" t="str">
         <v>MF Gut</v>
       </c>
+      <c r="O86" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P86" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q86" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R86" s="1">
+        <v>46071.45885416667</v>
       </c>
     </row>
     <row r="87">
@@ -4405,20 +4639,23 @@
       <c r="J87" t="str">
         <v>Angel Ann H. Vargas</v>
       </c>
-      <c r="M87" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N87" t="str">
+      <c r="L87" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M87" t="str">
         <v>Yeast (BSF)</v>
       </c>
-      <c r="O87" s="1">
+      <c r="N87" s="1">
         <v>45399.000497685185</v>
       </c>
+      <c r="O87" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P87" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q87" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R87" s="1">
+        <v>46071.458865740744</v>
       </c>
     </row>
     <row r="88">
@@ -4452,20 +4689,23 @@
       <c r="J88" t="str">
         <v>Anne-Nora N. Sabirin</v>
       </c>
-      <c r="M88" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N88" t="str">
+      <c r="L88" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M88" t="str">
         <v>Goat (Sabirin, MSU IIT)</v>
       </c>
-      <c r="O88" s="1">
+      <c r="N88" s="1">
         <v>45414.000497685185</v>
       </c>
+      <c r="O88" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P88" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q88" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R88" s="1">
+        <v>46071.458865740744</v>
       </c>
     </row>
     <row r="89">
@@ -4499,17 +4739,20 @@
       <c r="J89" t="str">
         <v>Clarnic A. Berbegal</v>
       </c>
-      <c r="M89" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N89" t="str">
+      <c r="L89" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M89" t="str">
         <v>RepPer SPIN</v>
       </c>
+      <c r="O89" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P89" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q89" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R89" s="1">
+        <v>46071.45888888889</v>
       </c>
     </row>
     <row r="90">
@@ -4543,20 +4786,23 @@
       <c r="J90" t="str">
         <v>Gavin Louie M. Amolo</v>
       </c>
-      <c r="M90" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N90" t="str">
+      <c r="L90" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M90" t="str">
         <v>Soil 16s (Siargao NHS)</v>
       </c>
-      <c r="O90" s="1">
+      <c r="N90" s="1">
         <v>45418.000497685185</v>
       </c>
+      <c r="O90" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P90" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q90" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R90" s="1">
+        <v>46071.45888888889</v>
       </c>
     </row>
     <row r="91">
@@ -4590,20 +4836,23 @@
       <c r="J91" t="str">
         <v>John Paul Resano</v>
       </c>
-      <c r="M91" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N91" t="str">
+      <c r="L91" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M91" t="str">
         <v>Salmonella sp.</v>
       </c>
-      <c r="O91" s="1">
+      <c r="N91" s="1">
         <v>45419.000497685185</v>
       </c>
+      <c r="O91" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P91" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q91" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R91" s="1">
+        <v>46071.45888888889</v>
       </c>
     </row>
     <row r="92">
@@ -4637,17 +4886,20 @@
       <c r="J92" t="str">
         <v>Dr. Jeannemar Genevive Y. Figueras</v>
       </c>
-      <c r="M92" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N92" t="str">
+      <c r="L92" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M92" t="str">
         <v>WVSU_16s Amplicon</v>
       </c>
+      <c r="O92" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P92" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q92" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R92" s="1">
+        <v>46071.45890046296</v>
       </c>
     </row>
     <row r="93">
@@ -4681,17 +4933,20 @@
       <c r="J93" t="str">
         <v>Carmelo del Castillo</v>
       </c>
-      <c r="M93" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N93" t="str">
+      <c r="L93" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M93" t="str">
         <v>CdC_Tilapia Mitogenome</v>
       </c>
+      <c r="O93" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P93" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q93" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R93" s="1">
+        <v>46071.45890046296</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
@@ -4726,20 +4981,23 @@
       <c r="J94" t="str">
         <v>Ryuya Matsuda</v>
       </c>
-      <c r="M94" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N94" t="str">
+      <c r="L94" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M94" t="str">
         <v>JIRCAS - Matsuda</v>
       </c>
-      <c r="O94" s="1">
+      <c r="N94" s="1">
         <v>45456.000497685185</v>
       </c>
+      <c r="O94" t="str">
+        <v>International</v>
+      </c>
       <c r="P94" t="str">
-        <v>International</v>
-      </c>
-      <c r="Q94" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R94" s="1">
+        <v>46071.45890046296</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
@@ -4774,20 +5032,23 @@
       <c r="J95" t="str">
         <v>Dencee Jean T. Ledesma</v>
       </c>
-      <c r="M95" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N95" t="str">
+      <c r="L95" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M95" t="str">
         <v>DOST VIP_Tomato WGS</v>
       </c>
-      <c r="O95" s="1">
+      <c r="N95" s="1">
         <v>45483.000497685185</v>
       </c>
+      <c r="O95" t="str">
+        <v>Government</v>
+      </c>
       <c r="P95" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q95" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R95" s="1">
+        <v>46071.45890046296</v>
       </c>
     </row>
     <row r="96">
@@ -4821,20 +5082,23 @@
       <c r="J96" t="str">
         <v>Noeme D. Pajarillo</v>
       </c>
-      <c r="M96" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N96" t="str">
+      <c r="L96" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M96" t="str">
         <v>Mussel eDNA</v>
       </c>
-      <c r="O96" s="1">
+      <c r="N96" s="1">
         <v>45491.000497685185</v>
       </c>
+      <c r="O96" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P96" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q96" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R96" s="1">
+        <v>46071.45894675926</v>
       </c>
     </row>
     <row r="97">
@@ -4868,20 +5132,23 @@
       <c r="J97" t="str">
         <v>Fermina Genson</v>
       </c>
-      <c r="M97" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N97" t="str">
+      <c r="L97" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M97" t="str">
         <v>VSU Larvae</v>
       </c>
-      <c r="O97" s="1">
+      <c r="N97" s="1">
         <v>45518.000497685185</v>
       </c>
+      <c r="O97" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P97" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q97" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R97" s="1">
+        <v>46071.45925925926</v>
       </c>
     </row>
     <row r="98">
@@ -4915,20 +5182,23 @@
       <c r="J98" t="str">
         <v>Fausto dela Cruz</v>
       </c>
-      <c r="M98" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N98" t="str">
+      <c r="L98" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M98" t="str">
         <v>iBest/inbreed</v>
       </c>
-      <c r="O98" s="1">
+      <c r="N98" s="1">
         <v>45531.000497685185</v>
       </c>
+      <c r="O98" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P98" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q98" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R98" s="1">
+        <v>46071.45925925926</v>
       </c>
     </row>
     <row r="99">
@@ -4962,19 +5232,19 @@
       <c r="J99" t="str">
         <v>DA-BAI</v>
       </c>
-      <c r="M99" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N99" t="str">
+      <c r="L99" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M99" t="str">
         <v>ASFV</v>
       </c>
-      <c r="O99" s="1">
+      <c r="N99" s="1">
         <v>45539.000497685185</v>
       </c>
+      <c r="O99" t="str">
+        <v>Government</v>
+      </c>
       <c r="P99" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q99" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -5009,20 +5279,23 @@
       <c r="J100" t="str">
         <v>Graziele Ann S. Taclas</v>
       </c>
-      <c r="M100" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N100" t="str">
+      <c r="L100" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M100" t="str">
         <v>UltraLow</v>
       </c>
-      <c r="O100" s="1">
+      <c r="N100" s="1">
         <v>45540.000497685185</v>
       </c>
+      <c r="O100" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P100" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q100" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R100" s="1">
+        <v>46071.45925925926</v>
       </c>
     </row>
     <row r="101">
@@ -5056,20 +5329,23 @@
       <c r="J101" t="str">
         <v>Vince Fuertes</v>
       </c>
-      <c r="M101" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N101" t="str">
+      <c r="L101" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M101" t="str">
         <v>Fuertes</v>
       </c>
-      <c r="O101" s="1">
+      <c r="N101" s="1">
         <v>45545.000497685185</v>
       </c>
+      <c r="O101" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P101" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q101" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R101" s="1">
+        <v>46071.45925925926</v>
       </c>
     </row>
     <row r="102">
@@ -5103,20 +5379,23 @@
       <c r="J102" t="str">
         <v>Jessa Cortes</v>
       </c>
-      <c r="M102" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N102" t="str">
+      <c r="L102" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M102" t="str">
         <v>Cortes</v>
       </c>
-      <c r="O102" s="1">
+      <c r="N102" s="1">
         <v>45545.000497685185</v>
       </c>
+      <c r="O102" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P102" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q102" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R102" s="1">
+        <v>46071.45927083334</v>
       </c>
     </row>
     <row r="103">
@@ -5150,19 +5429,19 @@
       <c r="J103" t="str">
         <v>Carmelo del Castillo</v>
       </c>
-      <c r="M103" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N103" t="str">
+      <c r="L103" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M103" t="str">
         <v>CdC_Catfish WGS</v>
       </c>
-      <c r="O103" s="1">
+      <c r="N103" s="1">
         <v>45554.000497685185</v>
       </c>
+      <c r="O103" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P103" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q103" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -5197,19 +5476,19 @@
       <c r="J104" t="str">
         <v>PGC Visayas</v>
       </c>
-      <c r="M104" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N104" t="str">
+      <c r="L104" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M104" t="str">
         <v>Universal Primers</v>
       </c>
-      <c r="O104" s="1">
+      <c r="N104" s="1">
         <v>45556.000497685185</v>
       </c>
+      <c r="O104" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P104" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q104" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -5244,19 +5523,19 @@
       <c r="J105" t="str">
         <v>PGC Visayas</v>
       </c>
-      <c r="M105" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N105" t="str">
+      <c r="L105" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M105" t="str">
         <v>AmpliSeq Optimization</v>
       </c>
-      <c r="O105" s="1">
+      <c r="N105" s="1">
         <v>45567.000497685185</v>
       </c>
+      <c r="O105" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P105" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q105" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -5291,17 +5570,20 @@
       <c r="J106" t="str">
         <v>Cedric Jay A. Nantong</v>
       </c>
-      <c r="M106" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N106" t="str">
+      <c r="L106" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M106" t="str">
         <v>UPV NEED PROJECT</v>
       </c>
+      <c r="O106" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P106" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q106" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R106" s="1">
+        <v>46071.45929398148</v>
       </c>
     </row>
     <row r="107">
@@ -5335,20 +5617,23 @@
       <c r="J107" t="str">
         <v>Jennifer S. Noveda</v>
       </c>
-      <c r="M107" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N107" t="str">
+      <c r="L107" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M107" t="str">
         <v>Fish Sauce</v>
       </c>
-      <c r="O107" s="1">
+      <c r="N107" s="1">
         <v>45609.000497685185</v>
       </c>
+      <c r="O107" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P107" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q107" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R107" s="1">
+        <v>46071.45929398148</v>
       </c>
     </row>
     <row r="108">
@@ -5382,20 +5667,23 @@
       <c r="J108" t="str">
         <v>Albaris Tahiluddin</v>
       </c>
-      <c r="M108" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N108" t="str">
+      <c r="L108" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M108" t="str">
         <v>Albaris</v>
       </c>
-      <c r="O108" s="1">
+      <c r="N108" s="1">
         <v>45610.000497685185</v>
       </c>
+      <c r="O108" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P108" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q108" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R108" s="1">
+        <v>46071.45929398148</v>
       </c>
     </row>
     <row r="109">
@@ -5429,17 +5717,20 @@
       <c r="J109" t="str">
         <v>Eric Zeus C. Rizo</v>
       </c>
-      <c r="M109" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N109" t="str">
+      <c r="L109" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M109" t="str">
         <v>Panay Metabarcoding</v>
       </c>
+      <c r="O109" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P109" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q109" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R109" s="1">
+        <v>46071.45929398148</v>
       </c>
     </row>
     <row r="110">
@@ -5473,20 +5764,23 @@
       <c r="J110" t="str">
         <v>Cid Jeriko Dadibalos</v>
       </c>
-      <c r="M110" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N110" t="str">
+      <c r="L110" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M110" t="str">
         <v>CID</v>
       </c>
-      <c r="O110" s="1">
+      <c r="N110" s="1">
         <v>45618.000497685185</v>
       </c>
+      <c r="O110" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P110" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q110" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R110" s="1">
+        <v>46071.45929398148</v>
       </c>
     </row>
     <row r="111">
@@ -5520,20 +5814,23 @@
       <c r="J111" t="str">
         <v>Dr. Mary Jane S. Apines-Amar</v>
       </c>
-      <c r="M111" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N111" t="str">
+      <c r="L111" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M111" t="str">
         <v>IBF-Tilapia</v>
       </c>
-      <c r="O111" s="1">
+      <c r="N111" s="1">
         <v>45623.000497685185</v>
       </c>
+      <c r="O111" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P111" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q111" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R111" s="1">
+        <v>46071.45929398148</v>
       </c>
     </row>
     <row r="112">
@@ -5567,20 +5864,23 @@
       <c r="J112" t="str">
         <v>Christian Jay Rosal</v>
       </c>
-      <c r="M112" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N112" t="str">
+      <c r="L112" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M112" t="str">
         <v>Microplastic</v>
       </c>
-      <c r="O112" s="1">
+      <c r="N112" s="1">
         <v>45624.000497685185</v>
       </c>
+      <c r="O112" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P112" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q112" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R112" s="1">
+        <v>46071.45930555555</v>
       </c>
     </row>
     <row r="113">
@@ -5614,20 +5914,23 @@
       <c r="J113" t="str">
         <v>Yuga Okamoto</v>
       </c>
-      <c r="M113" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N113" t="str">
+      <c r="L113" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M113" t="str">
         <v>Elops</v>
       </c>
-      <c r="O113" s="1">
+      <c r="N113" s="1">
         <v>45630.000497685185</v>
       </c>
+      <c r="O113" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P113" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q113" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R113" s="1">
+        <v>46071.45930555555</v>
       </c>
     </row>
     <row r="114">
@@ -5661,20 +5964,23 @@
       <c r="J114" t="str">
         <v>Christian Molina</v>
       </c>
-      <c r="M114" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N114" t="str">
+      <c r="L114" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M114" t="str">
         <v>Molina_Probiotics</v>
       </c>
-      <c r="O114" s="1">
+      <c r="N114" s="1">
         <v>45638.000497685185</v>
       </c>
+      <c r="O114" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P114" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q114" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R114" s="1">
+        <v>46071.45931712963</v>
       </c>
     </row>
     <row r="115">
@@ -5708,20 +6014,23 @@
       <c r="J115" t="str">
         <v>Gene Seneris</v>
       </c>
-      <c r="M115" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N115" t="str">
+      <c r="L115" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M115" t="str">
         <v>Abaca</v>
       </c>
-      <c r="O115" s="1">
+      <c r="N115" s="1">
         <v>45664.000497685185</v>
       </c>
+      <c r="O115" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P115" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q115" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R115" s="1">
+        <v>46071.45931712963</v>
       </c>
     </row>
     <row r="116">
@@ -5755,19 +6064,19 @@
       <c r="J116" t="str">
         <v>Stephanie Faith Apines</v>
       </c>
-      <c r="M116" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N116" t="str">
+      <c r="L116" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M116" t="str">
         <v>Perlas</v>
       </c>
-      <c r="O116" s="1">
+      <c r="N116" s="1">
         <v>45666.000497685185</v>
       </c>
+      <c r="O116" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P116" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q116" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -5802,20 +6111,23 @@
       <c r="J117" t="str">
         <v>Eunice Valad-on</v>
       </c>
-      <c r="M117" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N117" t="str">
+      <c r="L117" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M117" t="str">
         <v>Ulva</v>
       </c>
-      <c r="O117" s="1">
+      <c r="N117" s="1">
         <v>45684.000497685185</v>
       </c>
+      <c r="O117" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P117" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q117" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R117" s="1">
+        <v>46071.45931712963</v>
       </c>
     </row>
     <row r="118">
@@ -5849,19 +6161,19 @@
       <c r="J118" t="str">
         <v>PGC VISAYAS</v>
       </c>
-      <c r="M118" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N118" t="str">
+      <c r="L118" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M118" t="str">
         <v>Pangasius</v>
       </c>
-      <c r="O118" s="1">
+      <c r="N118" s="1">
         <v>45685.000497685185</v>
       </c>
+      <c r="O118" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P118" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q118" t="str">
         <v>Completed</v>
       </c>
     </row>
@@ -5896,20 +6208,23 @@
       <c r="J119" t="str">
         <v>Tiffany Xu</v>
       </c>
-      <c r="M119" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N119" t="str">
+      <c r="L119" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M119" t="str">
         <v>Xu</v>
       </c>
-      <c r="O119" s="1">
+      <c r="N119" s="1">
         <v>45700.000497685185</v>
       </c>
+      <c r="O119" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P119" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q119" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R119" s="1">
+        <v>46071.459328703706</v>
       </c>
     </row>
     <row r="120">
@@ -5943,20 +6258,23 @@
       <c r="J120" t="str">
         <v>Honnie Joy Balauro</v>
       </c>
-      <c r="M120" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N120" t="str">
+      <c r="L120" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M120" t="str">
         <v>Honnie</v>
       </c>
-      <c r="O120" s="1">
+      <c r="N120" s="1">
         <v>45707.000497685185</v>
       </c>
+      <c r="O120" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P120" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q120" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R120" s="1">
+        <v>46071.459328703706</v>
       </c>
     </row>
     <row r="121">
@@ -5990,20 +6308,23 @@
       <c r="J121" t="str">
         <v>Ferlyn Legarde</v>
       </c>
-      <c r="M121" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N121" t="str">
+      <c r="L121" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M121" t="str">
         <v>Meio</v>
       </c>
-      <c r="O121" s="1">
+      <c r="N121" s="1">
         <v>45708.000497685185</v>
       </c>
+      <c r="O121" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P121" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q121" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R121" s="1">
+        <v>46071.459340277775</v>
       </c>
     </row>
     <row r="122">
@@ -6037,20 +6358,23 @@
       <c r="J122" t="str">
         <v>Kyle Anthony C. Salinas</v>
       </c>
-      <c r="M122" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N122" t="str">
+      <c r="L122" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M122" t="str">
         <v>Thraustro</v>
       </c>
-      <c r="O122" s="1">
+      <c r="N122" s="1">
         <v>45712.000497685185</v>
       </c>
+      <c r="O122" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P122" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q122" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R122" s="1">
+        <v>46071.459340277775</v>
       </c>
     </row>
     <row r="123">
@@ -6084,19 +6408,19 @@
       <c r="J123" t="str">
         <v>Dr. Mary Jane S. Apines-Amar</v>
       </c>
-      <c r="M123" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N123" t="str">
-        <v/>
-      </c>
-      <c r="O123" s="1">
+      <c r="L123" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" s="1">
         <v>45741.000497685185</v>
       </c>
+      <c r="O123" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P123" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q123" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -6131,17 +6455,20 @@
       <c r="J124" t="str">
         <v>Jezel D. Alcantara</v>
       </c>
-      <c r="M124" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N124" t="str">
+      <c r="L124" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M124" t="str">
         <v>YY Male</v>
       </c>
+      <c r="O124" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P124" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q124" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R124" s="1">
+        <v>46071.459340277775</v>
       </c>
     </row>
     <row r="125">
@@ -6175,20 +6502,23 @@
       <c r="J125" t="str">
         <v>Dionie S. Barrientos</v>
       </c>
-      <c r="M125" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N125" t="str">
+      <c r="L125" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M125" t="str">
         <v>Pine</v>
       </c>
-      <c r="O125" s="1">
+      <c r="N125" s="1">
         <v>45742.000497685185</v>
       </c>
+      <c r="O125" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P125" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q125" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R125" s="1">
+        <v>46071.45935185185</v>
       </c>
     </row>
     <row r="126">
@@ -6222,20 +6552,23 @@
       <c r="J126" t="str">
         <v>Mary Claire Gatucao</v>
       </c>
-      <c r="M126" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N126" t="str">
+      <c r="L126" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M126" t="str">
         <v>Shipworm</v>
       </c>
-      <c r="O126" s="1">
+      <c r="N126" s="1">
         <v>45769.000497685185</v>
       </c>
+      <c r="O126" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P126" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q126" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R126" s="1">
+        <v>46071.45935185185</v>
       </c>
     </row>
     <row r="127">
@@ -6269,20 +6602,23 @@
       <c r="J127" t="str">
         <v>Maria Isabel Layson</v>
       </c>
-      <c r="M127" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N127" t="str">
+      <c r="L127" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M127" t="str">
         <v>Layson</v>
       </c>
-      <c r="O127" s="1">
+      <c r="N127" s="1">
         <v>45770.000497685185</v>
       </c>
+      <c r="O127" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P127" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q127" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R127" s="1">
+        <v>46071.45935185185</v>
       </c>
     </row>
     <row r="128" xml:space="preserve">
@@ -6317,20 +6653,23 @@
       <c r="J128" t="str">
         <v>Cheeny A. Honcada</v>
       </c>
-      <c r="M128" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N128" t="str">
+      <c r="L128" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M128" t="str">
         <v>Honcada</v>
       </c>
-      <c r="O128" s="1">
+      <c r="N128" s="1">
         <v>45771.000497685185</v>
       </c>
+      <c r="O128" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P128" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q128" t="str">
         <v>Cancelled</v>
+      </c>
+      <c r="R128" s="1">
+        <v>46071.45936342593</v>
       </c>
     </row>
     <row r="129">
@@ -6364,20 +6703,23 @@
       <c r="J129" t="str">
         <v>Kayla Marie F Parreño</v>
       </c>
-      <c r="M129" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N129" t="str">
+      <c r="L129" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M129" t="str">
         <v>Parreno</v>
       </c>
-      <c r="O129" s="1">
+      <c r="N129" s="1">
         <v>45772.000497685185</v>
       </c>
+      <c r="O129" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P129" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q129" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R129" s="1">
+        <v>46071.45936342593</v>
       </c>
     </row>
     <row r="130">
@@ -6411,20 +6753,23 @@
       <c r="J130" t="str">
         <v>Louie Altamia</v>
       </c>
-      <c r="M130" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N130" t="str">
+      <c r="L130" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M130" t="str">
         <v>Blastocystis</v>
       </c>
-      <c r="O130" s="1">
+      <c r="N130" s="1">
         <v>45796.000497685185</v>
       </c>
+      <c r="O130" t="str">
+        <v>Private/Local</v>
+      </c>
       <c r="P130" t="str">
-        <v>Private/Local</v>
-      </c>
-      <c r="Q130" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R130" s="1">
+        <v>46071.45936342593</v>
       </c>
     </row>
     <row r="131">
@@ -6458,20 +6803,23 @@
       <c r="J131" t="str">
         <v>Jelly D. Layda</v>
       </c>
-      <c r="M131" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N131" t="str">
+      <c r="L131" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M131" t="str">
         <v>Layda</v>
       </c>
-      <c r="O131" s="1">
+      <c r="N131" s="1">
         <v>45797.000497685185</v>
       </c>
+      <c r="O131" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P131" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q131" t="str">
-        <v>Completed</v>
+        <v>Completed</v>
+      </c>
+      <c r="R131" s="1">
+        <v>46071.459375</v>
       </c>
     </row>
     <row r="132">
@@ -6505,20 +6853,23 @@
       <c r="J132" t="str">
         <v>Ivy S. Arizapa</v>
       </c>
-      <c r="M132" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N132" t="str">
+      <c r="L132" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M132" t="str">
         <v>Arizapa</v>
       </c>
-      <c r="O132" s="1">
+      <c r="N132" s="1">
         <v>45828.000497685185</v>
       </c>
+      <c r="O132" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P132" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q132" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R132" s="1">
+        <v>46071.459386574075</v>
       </c>
     </row>
     <row r="133">
@@ -6552,19 +6903,19 @@
       <c r="J133" t="str">
         <v>Elsie Y. Guibone</v>
       </c>
-      <c r="M133" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N133" t="str">
+      <c r="L133" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M133" t="str">
         <v>Guibone</v>
       </c>
-      <c r="O133" s="1">
+      <c r="N133" s="1">
         <v>45831.000497685185</v>
       </c>
+      <c r="O133" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P133" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q133" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -6599,19 +6950,19 @@
       <c r="J134" t="str">
         <v>Vincent Jay H. Gado</v>
       </c>
-      <c r="M134" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N134" t="str">
+      <c r="L134" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M134" t="str">
         <v>Gado</v>
       </c>
-      <c r="O134" s="1">
+      <c r="N134" s="1">
         <v>45831.000497685185</v>
       </c>
+      <c r="O134" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P134" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q134" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -6646,20 +6997,23 @@
       <c r="J135" t="str">
         <v>Pee Jee Jareno</v>
       </c>
-      <c r="M135" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N135" t="str">
+      <c r="L135" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M135" t="str">
         <v>Jareno</v>
       </c>
-      <c r="O135" s="1">
+      <c r="N135" s="1">
         <v>45846.000497685185</v>
       </c>
+      <c r="O135" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P135" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q135" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R135" s="1">
+        <v>46071.459386574075</v>
       </c>
     </row>
     <row r="136">
@@ -6693,20 +7047,23 @@
       <c r="J136" t="str">
         <v>Allena Esther D. Arteta</v>
       </c>
-      <c r="M136" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N136" t="str">
+      <c r="L136" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M136" t="str">
         <v>Arteta</v>
       </c>
-      <c r="O136" s="1">
+      <c r="N136" s="1">
         <v>45852.000497685185</v>
       </c>
+      <c r="O136" t="str">
+        <v>N/A</v>
+      </c>
       <c r="P136" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="Q136" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R136" s="1">
+        <v>46071.459398148145</v>
       </c>
     </row>
     <row r="137">
@@ -6740,17 +7097,20 @@
       <c r="J137" t="str">
         <v>Kelee Ira B. Noque</v>
       </c>
-      <c r="M137" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N137" t="str">
+      <c r="L137" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M137" t="str">
         <v>Sedanza</v>
       </c>
+      <c r="O137" t="str">
+        <v>Government</v>
+      </c>
       <c r="P137" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q137" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R137" s="1">
+        <v>46071.459398148145</v>
       </c>
     </row>
     <row r="138">
@@ -6784,20 +7144,23 @@
       <c r="J138" t="str">
         <v>Sanda Tetsuya</v>
       </c>
-      <c r="M138" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N138" t="str">
+      <c r="L138" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M138" t="str">
         <v>Tetsuya</v>
       </c>
-      <c r="O138" s="1">
+      <c r="N138" s="1">
         <v>45904.000497685185</v>
       </c>
+      <c r="O138" t="str">
+        <v>International</v>
+      </c>
       <c r="P138" t="str">
-        <v>International</v>
-      </c>
-      <c r="Q138" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R138" s="1">
+        <v>46071.45940972222</v>
       </c>
     </row>
     <row r="139">
@@ -6831,20 +7194,23 @@
       <c r="J139" t="str">
         <v>Virgie Celestial</v>
       </c>
-      <c r="M139" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N139" t="str">
+      <c r="L139" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M139" t="str">
         <v>Celestial</v>
       </c>
-      <c r="O139" s="1">
+      <c r="N139" s="1">
         <v>45909.000497685185</v>
       </c>
+      <c r="O139" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P139" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q139" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R139" s="1">
+        <v>46071.45940972222</v>
       </c>
     </row>
     <row r="140">
@@ -6878,20 +7244,23 @@
       <c r="J140" t="str">
         <v>Joshua Y. Divinagracia</v>
       </c>
-      <c r="M140" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N140" t="str">
+      <c r="L140" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M140" t="str">
         <v>Divinagracia</v>
       </c>
-      <c r="O140" s="1">
+      <c r="N140" s="1">
         <v>45910.000497685185</v>
       </c>
+      <c r="O140" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P140" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q140" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R140" s="1">
+        <v>46071.45940972222</v>
       </c>
     </row>
     <row r="141">
@@ -6925,20 +7294,23 @@
       <c r="J141" t="str">
         <v>Kriz Sanchez Delos Reyes</v>
       </c>
-      <c r="M141" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N141" t="str">
+      <c r="L141" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M141" t="str">
         <v>NEMSU</v>
       </c>
-      <c r="O141" s="1">
+      <c r="N141" s="1">
         <v>45929.000497685185</v>
       </c>
+      <c r="O141" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P141" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q141" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R141" s="1">
+        <v>46071.4594212963</v>
       </c>
     </row>
     <row r="142">
@@ -6972,20 +7344,23 @@
       <c r="J142" t="str">
         <v>Adrienne Marrie S. Bugayon-Janagap</v>
       </c>
-      <c r="M142" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N142" t="str">
+      <c r="L142" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M142" t="str">
         <v xml:space="preserve"> </v>
       </c>
-      <c r="O142" s="1">
+      <c r="N142" s="1">
         <v>45929.000497685185</v>
       </c>
+      <c r="O142" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P142" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q142" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R142" s="1">
+        <v>46071.4594212963</v>
       </c>
     </row>
     <row r="143">
@@ -7019,19 +7394,19 @@
       <c r="J143" t="str">
         <v>Joshua Adrian A. Valdez</v>
       </c>
-      <c r="M143" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N143" t="str">
+      <c r="L143" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M143" t="str">
         <v>Valdez</v>
       </c>
-      <c r="O143" s="1">
+      <c r="N143" s="1">
         <v>45951.000497685185</v>
       </c>
+      <c r="O143" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P143" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q143" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -7066,19 +7441,19 @@
       <c r="J144" t="str">
         <v>Ma. Clarissa Tamon</v>
       </c>
-      <c r="M144" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N144" t="str">
+      <c r="L144" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M144" t="str">
         <v>Tamon</v>
       </c>
-      <c r="O144" s="1">
+      <c r="N144" s="1">
         <v>45958.000497685185</v>
       </c>
+      <c r="O144" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P144" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q144" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -7105,7 +7480,7 @@
         <v xml:space="preserve">jeeeaquino@up.edu.ph </v>
       </c>
       <c r="H145" t="str">
-        <v/>
+        <v>qPCR Pineapple</v>
       </c>
       <c r="I145" t="str">
         <v>DOST-ASTHRDP</v>
@@ -7113,20 +7488,23 @@
       <c r="J145" t="str">
         <v>Eunice Raiza Panagsagan</v>
       </c>
-      <c r="M145" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N145" t="str">
+      <c r="L145" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M145" t="str">
         <v>Panagsagan</v>
       </c>
-      <c r="O145" s="1">
+      <c r="N145" s="1">
         <v>45960.000497685185</v>
       </c>
+      <c r="O145" t="str">
+        <v>Government</v>
+      </c>
       <c r="P145" t="str">
-        <v/>
-      </c>
-      <c r="Q145" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R145" s="1">
+        <v>46071.4594212963</v>
       </c>
     </row>
     <row r="146">
@@ -7160,20 +7538,23 @@
       <c r="J146" t="str">
         <v>Francis Legario</v>
       </c>
-      <c r="M146" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N146" t="str">
+      <c r="L146" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M146" t="str">
         <v>OSMAC</v>
       </c>
-      <c r="O146" s="1">
+      <c r="N146" s="1">
         <v>45973.000497685185</v>
       </c>
+      <c r="O146" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P146" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q146" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R146" s="1">
+        <v>46071.4594212963</v>
       </c>
     </row>
     <row r="147">
@@ -7207,20 +7588,23 @@
       <c r="J147" t="str">
         <v>Jana Marie P. Dompor</v>
       </c>
-      <c r="M147" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N147" t="str">
+      <c r="L147" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M147" t="str">
         <v>Dompor</v>
       </c>
-      <c r="O147" s="1">
+      <c r="N147" s="1">
         <v>45985.000497685185</v>
       </c>
+      <c r="O147" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P147" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q147" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R147" s="1">
+        <v>46071.45943287037</v>
       </c>
     </row>
     <row r="148">
@@ -7254,20 +7638,23 @@
       <c r="J148" t="str">
         <v>Sealthiel Andrei Malones</v>
       </c>
-      <c r="M148" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N148" t="str">
+      <c r="L148" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M148" t="str">
         <v>Malones</v>
       </c>
-      <c r="O148" s="1">
+      <c r="N148" s="1">
         <v>45992.000497685185</v>
       </c>
+      <c r="O148" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P148" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q148" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R148" s="1">
+        <v>46071.45943287037</v>
       </c>
     </row>
     <row r="149">
@@ -7301,16 +7688,16 @@
       <c r="J149" t="str">
         <v>Mary Nia M. Santos</v>
       </c>
-      <c r="M149" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N149" t="str">
+      <c r="L149" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M149" t="str">
         <v>Santos</v>
       </c>
+      <c r="O149" t="str">
+        <v>Government</v>
+      </c>
       <c r="P149" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q149" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -7345,20 +7732,23 @@
       <c r="J150" t="str">
         <v>Eugene Earl P. Drua</v>
       </c>
-      <c r="M150" s="1">
-        <v>45884.000497685185</v>
-      </c>
-      <c r="N150" t="str">
+      <c r="L150" s="1">
+        <v>45884.000497685185</v>
+      </c>
+      <c r="M150" t="str">
         <v>Drua</v>
       </c>
-      <c r="O150" s="1">
+      <c r="N150" s="1">
         <v>46000.000497685185</v>
       </c>
+      <c r="O150" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P150" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q150" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R150" s="1">
+        <v>46071.459444444445</v>
       </c>
     </row>
     <row r="151">
@@ -7392,20 +7782,23 @@
       <c r="J151" t="str">
         <v>VMENF</v>
       </c>
-      <c r="M151" s="1">
+      <c r="L151" s="1">
         <v>46030.62136574074</v>
       </c>
-      <c r="N151" t="str">
+      <c r="M151" t="str">
         <v>Fish 205</v>
       </c>
-      <c r="O151" s="1">
+      <c r="N151" s="1">
         <v>46002.33383101852</v>
       </c>
+      <c r="O151" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P151" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q151" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R151" s="1">
+        <v>46071.459444444445</v>
       </c>
     </row>
     <row r="152">
@@ -7439,20 +7832,23 @@
       <c r="J152" t="str">
         <v>N/A</v>
       </c>
-      <c r="M152" s="1">
+      <c r="L152" s="1">
         <v>46030.624710648146</v>
       </c>
-      <c r="N152" t="str">
+      <c r="M152" t="str">
         <v>Retail</v>
       </c>
-      <c r="O152" s="1">
+      <c r="N152" s="1">
         <v>46006.33383101852</v>
       </c>
+      <c r="O152" t="str">
+        <v>Government</v>
+      </c>
       <c r="P152" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q152" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R152" s="1">
+        <v>46071.459444444445</v>
       </c>
     </row>
     <row r="153">
@@ -7486,20 +7882,23 @@
       <c r="J153" t="str">
         <v>Lee Genesis S. Mabaquiao</v>
       </c>
-      <c r="M153" s="1">
+      <c r="L153" s="1">
         <v>46030.626284722224</v>
       </c>
-      <c r="N153" t="str">
+      <c r="M153" t="str">
         <v>Banga</v>
       </c>
-      <c r="O153" s="1">
+      <c r="N153" s="1">
         <v>46002.33383101852</v>
       </c>
+      <c r="O153" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P153" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q153" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R153" s="1">
+        <v>46071.459444444445</v>
       </c>
     </row>
     <row r="154">
@@ -7533,20 +7932,23 @@
       <c r="J154" t="str">
         <v>Mary Dianne Grace Bahuad</v>
       </c>
-      <c r="M154" s="1">
+      <c r="L154" s="1">
         <v>46030.62844907407</v>
       </c>
-      <c r="N154" t="str">
+      <c r="M154" t="str">
         <v>SEAFDEC</v>
       </c>
-      <c r="O154" s="1">
+      <c r="N154" s="1">
         <v>46008.33383101852</v>
       </c>
+      <c r="O154" t="str">
+        <v>Government</v>
+      </c>
       <c r="P154" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q154" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R154" s="1">
+        <v>46071.459444444445</v>
       </c>
     </row>
     <row r="155">
@@ -7580,19 +7982,19 @@
       <c r="J155" t="str">
         <v>N/A</v>
       </c>
-      <c r="M155" s="1">
+      <c r="L155" s="1">
         <v>46030.67076388889</v>
       </c>
-      <c r="N155" t="str">
+      <c r="M155" t="str">
         <v>USLS-David</v>
       </c>
-      <c r="O155" s="1">
+      <c r="N155" s="1">
         <v>46030.000497685185</v>
       </c>
+      <c r="O155" t="str">
+        <v>Government</v>
+      </c>
       <c r="P155" t="str">
-        <v>Government</v>
-      </c>
-      <c r="Q155" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -7604,7 +8006,7 @@
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>K5532K7Y4gIFDrjLdCUi</v>
+        <v>1iu9FNaI6nnJ54k8qYTJ</v>
       </c>
       <c r="D156">
         <v>2026</v>
@@ -7627,20 +8029,23 @@
       <c r="J156" t="str">
         <v>N/A</v>
       </c>
-      <c r="M156" s="1">
+      <c r="L156" s="1">
         <v>46031.66804398148</v>
       </c>
-      <c r="N156" t="str">
+      <c r="M156" t="str">
         <v>Saripada</v>
       </c>
-      <c r="O156" s="1">
+      <c r="N156" s="1">
         <v>46031.000497685185</v>
       </c>
+      <c r="O156" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P156" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q156" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R156" s="1">
+        <v>46071.45945601852</v>
       </c>
     </row>
     <row r="157">
@@ -7674,19 +8079,19 @@
       <c r="J157" t="str">
         <v>N/A</v>
       </c>
-      <c r="M157" s="1">
+      <c r="L157" s="1">
         <v>46035.90226851852</v>
       </c>
-      <c r="N157" t="str">
+      <c r="M157" t="str">
         <v>USLS-Pilarta</v>
       </c>
-      <c r="O157" s="1">
+      <c r="N157" s="1">
         <v>46035.000497685185</v>
       </c>
+      <c r="O157" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P157" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q157" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -7721,16 +8126,19 @@
       <c r="J158" t="str">
         <v>N/A</v>
       </c>
-      <c r="N158" t="str">
+      <c r="L158" s="1">
+        <v>46035.897141203706</v>
+      </c>
+      <c r="M158" t="str">
         <v>Salvador</v>
       </c>
-      <c r="O158" s="1">
+      <c r="N158" s="1">
         <v>46036.33383101852</v>
       </c>
+      <c r="O158" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P158" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q158" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -7765,19 +8173,19 @@
       <c r="J159" t="str">
         <v>N/A</v>
       </c>
-      <c r="M159" s="1">
+      <c r="L159" s="1">
         <v>46041.52255787037</v>
       </c>
-      <c r="N159" t="str">
+      <c r="M159" t="str">
         <v>USLS-Pediongco</v>
       </c>
-      <c r="O159" s="1">
+      <c r="N159" s="1">
         <v>46041.33383101852</v>
       </c>
+      <c r="O159" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P159" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q159" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -7812,19 +8220,19 @@
       <c r="J160" t="str">
         <v>VMENF</v>
       </c>
-      <c r="M160" s="1">
+      <c r="L160" s="1">
         <v>46042.37255787037</v>
       </c>
-      <c r="N160" t="str">
+      <c r="M160" t="str">
         <v>Comorro</v>
       </c>
-      <c r="O160" s="1">
+      <c r="N160" s="1">
         <v>46042.33383101852</v>
       </c>
+      <c r="O160" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P160" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q160" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -7859,20 +8267,23 @@
       <c r="J161" t="str">
         <v>VMENF</v>
       </c>
-      <c r="M161" s="1">
+      <c r="L161" s="1">
         <v>46042.3758912037</v>
       </c>
-      <c r="N161" t="str">
+      <c r="M161" t="str">
         <v>Aquaculture Feeds Metabarcoding</v>
       </c>
-      <c r="O161" s="1">
+      <c r="N161" s="1">
         <v>46042.33383101852</v>
       </c>
+      <c r="O161" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P161" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q161" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R161" s="1">
+        <v>46071.45947916667</v>
       </c>
     </row>
     <row r="162">
@@ -7906,20 +8317,23 @@
       <c r="J162" t="str">
         <v>Francis Legario</v>
       </c>
-      <c r="M162" s="1">
+      <c r="L162" s="1">
         <v>46048.639548611114</v>
       </c>
-      <c r="N162" t="str">
+      <c r="M162" t="str">
         <v>ISAT-AMR</v>
       </c>
-      <c r="O162" s="1">
+      <c r="N162" s="1">
         <v>46048.33383101852</v>
       </c>
+      <c r="O162" t="str">
+        <v>SUC/HEI</v>
+      </c>
       <c r="P162" t="str">
-        <v>SUC/HEI</v>
-      </c>
-      <c r="Q162" t="str">
         <v>Ongoing</v>
+      </c>
+      <c r="R162" s="1">
+        <v>46071.45949074074</v>
       </c>
     </row>
     <row r="163">
@@ -7953,19 +8367,19 @@
       <c r="J163" t="str">
         <v>VMENF</v>
       </c>
-      <c r="M163" s="1">
+      <c r="L163" s="1">
         <v>46050.405185185184</v>
       </c>
-      <c r="N163" t="str">
+      <c r="M163" t="str">
         <v>EU-Naria</v>
       </c>
-      <c r="O163" s="1">
+      <c r="N163" s="1">
         <v>46050.33383101852</v>
       </c>
+      <c r="O163" t="str">
+        <v>UP System</v>
+      </c>
       <c r="P163" t="str">
-        <v>UP System</v>
-      </c>
-      <c r="Q163" t="str">
         <v>Ongoing</v>
       </c>
     </row>
@@ -8000,25 +8414,154 @@
       <c r="J164" t="str">
         <v>Joana Joy Huervana</v>
       </c>
-      <c r="M164" s="1">
+      <c r="L164" s="1">
         <v>46058.506840277776</v>
       </c>
-      <c r="N164" t="str">
+      <c r="M164" t="str">
         <v>SEAFDEC-Lobster</v>
       </c>
-      <c r="O164" s="1">
+      <c r="N164" s="1">
         <v>46058.33383101852</v>
       </c>
+      <c r="O164" t="str">
+        <v>International</v>
+      </c>
       <c r="P164" t="str">
-        <v>International</v>
-      </c>
-      <c r="Q164" t="str">
         <v>Ongoing</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>P-2026-011</v>
+      </c>
+      <c r="B165" t="str">
+        <v/>
+      </c>
+      <c r="C165" t="str">
+        <v>20hmj3FcBHjg6dvVG465</v>
+      </c>
+      <c r="D165">
+        <v>2026</v>
+      </c>
+      <c r="E165" t="str">
+        <v>External</v>
+      </c>
+      <c r="F165" t="str">
+        <v>P-2026-011</v>
+      </c>
+      <c r="G165" t="str">
+        <v>Lee Genesis S. Mabaquiao</v>
+      </c>
+      <c r="H165" t="str">
+        <v>Antibacterial Efficacy and Whole-Genome Analysis of Methicillin-Resistant Staphylococcus aureus (ATCC-BAA-1708) TREATED WITH  SS25 ETHANOLIC LEAF EXTRACT</v>
+      </c>
+      <c r="I165" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J165" t="str">
+        <v>Chris Armand N. Santiana</v>
+      </c>
+      <c r="L165" s="1">
+        <v>46062.65466435185</v>
+      </c>
+      <c r="M165" t="str">
+        <v>USA-WGS</v>
+      </c>
+      <c r="N165" s="1">
+        <v>46062.33383101852</v>
+      </c>
+      <c r="O165" t="str">
+        <v>Private/Local</v>
+      </c>
+      <c r="P165" t="str">
+        <v>Ongoing</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>P-2026-012</v>
+      </c>
+      <c r="B166" t="str">
+        <v/>
+      </c>
+      <c r="C166" t="str">
+        <v>PTWl9Um7aLNNrAoPsPGR</v>
+      </c>
+      <c r="D166">
+        <v>2026</v>
+      </c>
+      <c r="E166" t="str">
+        <v>External</v>
+      </c>
+      <c r="F166" t="str">
+        <v>P-2026-012</v>
+      </c>
+      <c r="G166" t="str">
+        <v>Jasmine C. Velo</v>
+      </c>
+      <c r="H166" t="str">
+        <v xml:space="preserve">Systematics of Marine Fungi in the Philippines </v>
+      </c>
+      <c r="I166" t="str">
+        <v>EB Gareth Jones</v>
+      </c>
+      <c r="J166" t="str">
+        <v>Mark C. Calabon</v>
+      </c>
+      <c r="L166" s="1">
+        <v>46063.56553240741</v>
+      </c>
+      <c r="M166" t="str">
+        <v>SMFP</v>
+      </c>
+      <c r="N166" s="1">
+        <v>46063.33383101852</v>
+      </c>
+      <c r="O166" t="str">
+        <v>UP System</v>
+      </c>
+      <c r="P166" t="str">
+        <v>Ongoing</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>P-2026-014</v>
+      </c>
+      <c r="C167" t="str">
+        <v>M5zczEbmOZPSTWrBKz5Q</v>
+      </c>
+      <c r="F167" t="str">
+        <v>P-2026-014</v>
+      </c>
+      <c r="H167" t="str">
+        <v>VSD eDNA</v>
+      </c>
+      <c r="I167" t="str">
+        <v>OVCRE</v>
+      </c>
+      <c r="L167" s="1">
+        <v>46076.461377314816</v>
+      </c>
+      <c r="N167" s="1">
+        <v>46076.43431712963</v>
+      </c>
+      <c r="O167" t="str">
+        <v>UP System</v>
+      </c>
+      <c r="P167" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="R167" s="1">
+        <v>46076.461377314816</v>
+      </c>
+      <c r="S167" t="str">
+        <v>Carmel Javier</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q164"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S167"/>
   </ignoredErrors>
 </worksheet>
 </file>